--- a/data/trans_orig/IP16A08-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A08-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5407</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7454</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16641</t>
+          <t>16668</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21409</t>
+          <t>21415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15127</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34851</t>
+          <t>34099</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40946</t>
+          <t>40942</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10318</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22282</t>
+          <t>22143</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11877</t>
+          <t>11896</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23646</t>
+          <t>23748</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24840</t>
+          <t>25736</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41713</t>
+          <t>41858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58425</t>
+          <t>58564</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>70389</t>
+          <t>70554</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64023</t>
+          <t>63921</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75792</t>
+          <t>75773</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126663</t>
+          <t>126518</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>143536</t>
+          <t>142640</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>84,72%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>639</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8832</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11240</t>
+          <t>12136</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>17126</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21914</t>
+          <t>21912</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26505</t>
+          <t>26434</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33219</t>
+          <t>33359</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46576</t>
+          <t>45680</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54956</t>
+          <t>54311</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>12958</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26859</t>
+          <t>26910</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17136</t>
+          <t>17273</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31439</t>
+          <t>31294</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33289</t>
+          <t>33252</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52817</t>
+          <t>53947</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98446</t>
+          <t>98395</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111893</t>
+          <t>112347</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111754</t>
+          <t>111899</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126057</t>
+          <t>125920</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>215681</t>
+          <t>214551</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>235209</t>
+          <t>235246</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,62%</t>
         </is>
       </c>
     </row>
@@ -2336,62 +2336,62 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5477</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,25%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5623</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,56%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4665</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4420</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16958</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>22009</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,49 +2464,49 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>97,47%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>16141</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>12835</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>92,24%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>73,34%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16141</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13080</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17500</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,24%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>74,74%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>52</t>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32370</t>
+          <t>32831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38762</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>7610</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18576</t>
+          <t>18432</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18871</t>
+          <t>19701</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17694</t>
+          <t>18901</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32286</t>
+          <t>33921</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69660</t>
+          <t>69804</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80777</t>
+          <t>80626</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82163</t>
+          <t>81333</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>93235</t>
+          <t>93482</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>156984</t>
+          <t>155349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>171576</t>
+          <t>170369</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,01%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10851</t>
+          <t>11354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15118</t>
+          <t>15740</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29205</t>
+          <t>28785</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35118</t>
+          <t>35130</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28582</t>
+          <t>28079</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36637</t>
+          <t>36599</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60718</t>
+          <t>60096</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>70186</t>
+          <t>70470</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11969</t>
+          <t>12225</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25357</t>
+          <t>25543</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13322</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27433</t>
+          <t>28594</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28536</t>
+          <t>28961</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47421</t>
+          <t>47480</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121864</t>
+          <t>121678</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>135252</t>
+          <t>134996</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>130533</t>
+          <t>129372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>144644</t>
+          <t>143842</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>257766</t>
+          <t>257707</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>276651</t>
+          <t>276226</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,51%</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5583</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20813</t>
+          <t>20964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19438</t>
+          <t>19129</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21340</t>
+          <t>21312</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36920</t>
+          <t>36045</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63541</t>
+          <t>63850</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74922</t>
+          <t>74936</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64280</t>
+          <t>64308</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76287</t>
+          <t>76115</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>131679</t>
+          <t>132554</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>148355</t>
+          <t>147939</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>696</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12588</t>
+          <t>12294</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19796</t>
+          <t>20299</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27029</t>
+          <t>27015</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>22577</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28165</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45073</t>
+          <t>45367</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>54004</t>
+          <t>53899</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,48%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>11815</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25387</t>
+          <t>24797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11902</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25702</t>
+          <t>25464</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27028</t>
+          <t>27336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45709</t>
+          <t>45555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102074</t>
+          <t>102664</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115485</t>
+          <t>115646</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97574</t>
+          <t>97812</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>111374</t>
+          <t>111171</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>205028</t>
+          <t>205182</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>223709</t>
+          <t>223401</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,1%</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25614</t>
+          <t>25096</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18544</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21391</t>
+          <t>21087</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32814</t>
+          <t>33797</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>102299</t>
+          <t>103338</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>116695</t>
+          <t>116953</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>98633</t>
+          <t>98937</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112025</t>
+          <t>112166</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>208053</t>
+          <t>207070</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>226530</t>
+          <t>227384</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1792</t>
+          <t>1753</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9298</t>
+          <t>9341</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4321</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14347</t>
+          <t>14581</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32344</t>
+          <t>32301</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39850</t>
+          <t>39889</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>38280</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45111</t>
+          <t>45164</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73806</t>
+          <t>73572</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83832</t>
+          <t>83490</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23123</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6591,7 +6591,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>11891</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27454</t>
+          <t>27497</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22666</t>
+          <t>23828</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45449</t>
+          <t>45074</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154592</t>
+          <t>155193</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>169939</t>
+          <t>169936</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>154747</t>
+          <t>154704</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170348</t>
+          <t>170310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314467</t>
+          <t>314842</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>337250</t>
+          <t>336088</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A08-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16A08-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1663</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5203</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,21%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>25,68%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5380</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5437</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>9,1%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1663</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5774</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,21%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>7645</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18595</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15055</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,79%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>74,32%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>20041</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16668</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21415</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16611</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>21407</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>90,9%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,6%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,13%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18595</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>14484</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,79%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34099</t>
+          <t>34660</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40942</t>
+          <t>40931</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20258</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22048</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>20258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17231</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12197</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>24272</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,91%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>15313</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>10153</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>22143</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9993</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>21500</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>18,97%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12,58%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>27,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>17231</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>11896</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>23748</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>19,65%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25736</t>
+          <t>24668</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41858</t>
+          <t>41204</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,47%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>70438</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>63397</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>75472</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>80,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>72,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,09%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>65394</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>58564</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>70554</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>59207</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>70714</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>81,03%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>72,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>87,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>70438</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>63921</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>75773</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>80,35%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126518</t>
+          <t>127172</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>142640</t>
+          <t>143708</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>87669</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>80707</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>87669</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,107 +1409,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4517</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2134</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9010</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,55%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2047</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>639</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5425</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5401</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,08%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>2,83%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,06%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4517</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8832</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>12,81%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>23,95%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>6563</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>3125</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>11133</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>11,35%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>5,41%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>25,04%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>6563</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>3505</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>12136</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -1522,107 +1522,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30749</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26256</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>33132</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>74,45%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>93,95%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>20504</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>17126</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>17150</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>21912</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>90,92%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,94%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>76,05%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>97,17%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>30749</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>26434</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>33359</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>87,19%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>74,96%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>51253</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>46683</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>54691</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>88,65%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>80,74%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
         <is>
           <t>94,59%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>51253</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>45680</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>54311</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>88,65%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>79,01%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>35266</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22551</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>35266</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23411</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17054</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>31611</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,08%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>19366</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12958</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>26910</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>13711</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>27978</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15,45%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>23411</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>17273</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>31294</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>16,35%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33252</t>
+          <t>34432</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53947</t>
+          <t>55159</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>119782</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>111582</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>126139</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,92%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,09%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>105939</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>98395</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>112347</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>97327</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>111594</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>84,55%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>78,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>119782</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>111899</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>125920</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>83,65%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>214551</t>
+          <t>213339</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>235246</t>
+          <t>234066</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,18%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>143193</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>143193</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,44%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2159</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>572</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5477</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5619</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>9,56%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4665</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1399</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16141</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13398</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>92,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>76,56%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>20422</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>17104</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>22009</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16962</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>22021</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>90,44%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>16141</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>12835</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17500</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>92,24%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32831</t>
+          <t>32159</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38682</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17500</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>22581</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>22581</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>22581</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>17500</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>17500</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>17500</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12605</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7764</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18669</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,48%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>12237</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7610</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18432</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7515</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>18647</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>13,87%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,89%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12605</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7552</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>19701</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18901</t>
+          <t>18079</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33921</t>
+          <t>33276</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>88429</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>82365</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>93270</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,52%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>81,52%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,32%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>75999</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>69804</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>80626</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>69589</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>80721</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>86,13%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,38%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>88429</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>81333</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>93482</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>87,52%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>155349</t>
+          <t>155994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>170369</t>
+          <t>171191</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,45%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>101034</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>88236</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>88236</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>88236</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>101034</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6080</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2995</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10630</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,42%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3363</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7619</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1304</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,24%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,93%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>6080</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>11354</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>15,42%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15740</t>
+          <t>15080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -3130,67 +3130,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>33353</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>28803</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>36438</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>84,58%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>73,04%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>33041</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>28785</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>35130</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>29298</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>35100</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>90,76%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>79,07%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>33353</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>28079</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>36599</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>84,58%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60096</t>
+          <t>60756</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>70470</t>
+          <t>70422</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>39433</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>36404</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>39433</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>20044</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13676</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27640</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,5%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>17758</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12225</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>25543</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>11906</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>25693</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,06%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17,35%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>20044</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>14124</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>28594</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28961</t>
+          <t>28283</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47480</t>
+          <t>49257</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>137922</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>130326</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>144290</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,31%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>82,5%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,34%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>129463</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>121678</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>134996</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>121528</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>135315</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>87,94%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>82,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>137922</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>129372</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>143842</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>87,31%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>257707</t>
+          <t>255930</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>276226</t>
+          <t>276904</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>147221</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,107 +3929,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3729</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>42,45%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>791</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3203</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4248</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>36,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>791</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3513</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -4042,74 +4042,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7995</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>57,55%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7995</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>5583</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>63,55%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>33</t>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20964</t>
+          <t>20229</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8786</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15691</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8786</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14752</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9701</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21588</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,23%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,33%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25,21%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>13011</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8043</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19129</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7775</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>18692</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>15,68%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,69%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>23,05%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>14752</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9505</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>21312</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20660</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36045</t>
+          <t>36915</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>70868</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>64032</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>75919</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>82,77%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74,79%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,67%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>69968</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>63850</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>74936</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>64287</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>75204</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>84,32%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>76,95%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>70868</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>64308</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>76115</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>82,77%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>132554</t>
+          <t>131684</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>147939</t>
+          <t>148464</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>88,06%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85620</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>82979</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85620</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6115</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,46%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,18%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4613</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1777</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8493</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8843</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>16,02%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2732</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>696</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6293</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12294</t>
+          <t>12638</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -4733,67 +4733,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>26138</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22755</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>28174</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>90,54%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>78,82%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>24179</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20299</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27015</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>19949</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>26798</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>83,98%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>70,5%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>93,83%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>26138</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>22577</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>28174</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>90,54%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45367</t>
+          <t>45023</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53899</t>
+          <t>53840</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,37%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28870</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>28792</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>28870</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>18275</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12814</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25905</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,39%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>17623</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11815</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>24797</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>12002</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>25156</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,83%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,45%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>18275</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>12105</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>25464</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,82%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27336</t>
+          <t>27656</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45555</t>
+          <t>49384</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>105001</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>97371</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>110462</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>78,99%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,61%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>109838</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>102664</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>115646</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>102305</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>115459</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>86,17%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80,55%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,73%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>105001</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>97812</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>111171</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>85,18%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>205182</t>
+          <t>201353</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>223401</t>
+          <t>223081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,107 +5532,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5043</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,85%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>36,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1655</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5318</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10,56%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5460</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>6,37%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>33,94%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1655</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5801</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -5645,74 +5645,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>12410</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>8877</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,15%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>63,77%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>9781</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>14012</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10349</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>15667</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>89,44%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>66,06%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>34</t>
@@ -5720,27 +5720,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>29242</t>
+          <t>22191</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25096</t>
+          <t>18241</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>76,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13920</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15230</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15667</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30897</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12194</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7049</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19419</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10312</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3890</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17505</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,49%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13265</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>6221</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21087</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>23577</t>
+          <t>22769</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>16063</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33797</t>
+          <t>32849</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>95718</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>88493</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>100863</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,7%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>82,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,47%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>110531</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>103338</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>116953</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>91,47%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,78%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>106759</t>
+          <t>82109</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>98937</t>
+          <t>74683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>112166</t>
+          <t>86463</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>217290</t>
+          <t>177827</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>207070</t>
+          <t>167747</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>227384</t>
+          <t>184533</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>107912</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>120843</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120024</t>
+          <t>92684</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>240867</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3378</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1242</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7534</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,47%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4674</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1753</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9341</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8231</t>
+          <t>9798</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14581</t>
+          <t>14425</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>39741</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>35585</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>41877</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,16%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,53%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>36968</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>32301</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>39889</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>88,78%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>77,57%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42822</t>
+          <t>35610</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38280</t>
+          <t>30729</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45164</t>
+          <t>38335</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>79790</t>
+          <t>75352</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>73572</t>
+          <t>69222</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83490</t>
+          <t>79366</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43119</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>41642</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46511</t>
+          <t>40527</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88153</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>17083</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>11064</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>25466</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,44%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>14986</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7779</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>22522</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,38%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11891</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27497</t>
+          <t>23447</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>33595</t>
+          <t>32574</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23828</t>
+          <t>23936</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45074</t>
+          <t>42490</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>147869</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>139486</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>153888</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,56%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>162729</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>155193</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>169936</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>91,57%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,62%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>163592</t>
+          <t>127500</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>154704</t>
+          <t>119545</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>170310</t>
+          <t>133259</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>326321</t>
+          <t>275370</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>314842</t>
+          <t>265454</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>336088</t>
+          <t>284008</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
